--- a/vol_surface1000.xlsx
+++ b/vol_surface1000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuJingjian\Spyder_files\equity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880A5F4E-3EA5-4919-BE59-A85783F7B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF77F579-EF64-47CB-AD16-BD37D051C8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -151,11 +151,11 @@
     <tableColumn id="32" xr3:uid="{0234EE59-ABF2-481B-9038-009D0B31379E}" name="col31"/>
     <tableColumn id="33" xr3:uid="{4F42D9BB-000F-40E8-B875-738D3BED2A2C}" name="col32"/>
     <tableColumn id="34" xr3:uid="{F6949971-92B9-4E16-AD99-6B67AEE467D5}" name="col33"/>
-    <tableColumn id="35" xr3:uid="{460A4676-5C2A-4433-BB6E-F62398555782}" name="col34"/>
-    <tableColumn id="36" xr3:uid="{14F1E3CA-BF80-42D8-9ADA-2378F9E1544B}" name="Column1"/>
-    <tableColumn id="37" xr3:uid="{BA198144-7768-413D-A3A3-7002EA597E73}" name="Column2"/>
-    <tableColumn id="38" xr3:uid="{0643CC29-EA59-4D3B-AACA-FBDA210F5C8D}" name="Column3"/>
-    <tableColumn id="39" xr3:uid="{567FFB73-6C98-4588-A1E8-10C463BF72B1}" name="Column4"/>
+    <tableColumn id="35" xr3:uid="{37E0BA91-E985-4789-A4CB-9941899D6365}" name="Column1"/>
+    <tableColumn id="36" xr3:uid="{08DAC5DC-0BC8-4516-A92D-B6DB1DE444C6}" name="Column2"/>
+    <tableColumn id="37" xr3:uid="{123C34B4-4EEB-47A9-9BBB-64C7D88A2912}" name="Column3"/>
+    <tableColumn id="38" xr3:uid="{EDB382FC-C885-4C06-A63A-EA6F090BA619}" name="Column4"/>
+    <tableColumn id="39" xr3:uid="{85DB0173-3F5B-404A-A634-9C838591D81D}" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -427,112 +427,112 @@
         <v>0</v>
       </c>
       <c r="B1">
+        <v>5600</v>
+      </c>
+      <c r="C1">
+        <v>5700</v>
+      </c>
+      <c r="D1">
+        <v>5800</v>
+      </c>
+      <c r="E1">
+        <v>5900</v>
+      </c>
+      <c r="F1">
+        <v>6000</v>
+      </c>
+      <c r="G1">
+        <v>6100</v>
+      </c>
+      <c r="H1">
         <v>6200</v>
       </c>
-      <c r="C1">
+      <c r="I1">
         <v>6300</v>
       </c>
-      <c r="D1">
+      <c r="J1">
         <v>6400</v>
       </c>
-      <c r="E1">
+      <c r="K1">
         <v>6500</v>
       </c>
-      <c r="F1">
+      <c r="L1">
         <v>6600</v>
       </c>
-      <c r="G1">
+      <c r="M1">
         <v>6700</v>
       </c>
-      <c r="H1">
+      <c r="N1">
         <v>6800</v>
       </c>
-      <c r="I1">
+      <c r="O1">
         <v>6900</v>
       </c>
-      <c r="J1">
+      <c r="P1">
         <v>7000</v>
       </c>
-      <c r="K1">
+      <c r="Q1">
         <v>7100</v>
       </c>
-      <c r="L1">
+      <c r="R1">
         <v>7200</v>
       </c>
-      <c r="M1">
+      <c r="S1">
         <v>7300</v>
       </c>
-      <c r="N1">
+      <c r="T1">
         <v>7400</v>
       </c>
-      <c r="O1">
+      <c r="U1">
         <v>7500</v>
       </c>
-      <c r="P1">
+      <c r="V1">
         <v>7600</v>
       </c>
-      <c r="Q1">
+      <c r="W1">
         <v>7700</v>
       </c>
-      <c r="R1">
+      <c r="X1">
         <v>7800</v>
       </c>
-      <c r="S1">
+      <c r="Y1">
         <v>7900</v>
       </c>
-      <c r="T1">
+      <c r="Z1">
         <v>8000</v>
       </c>
-      <c r="U1">
+      <c r="AA1">
         <v>8100</v>
       </c>
-      <c r="V1">
+      <c r="AB1">
         <v>8200</v>
       </c>
-      <c r="W1">
+      <c r="AC1">
         <v>8300</v>
       </c>
-      <c r="X1">
+      <c r="AD1">
         <v>8400</v>
       </c>
-      <c r="Y1">
+      <c r="AE1">
         <v>8500</v>
       </c>
-      <c r="Z1">
+      <c r="AF1">
         <v>8600</v>
       </c>
-      <c r="AA1">
-        <v>8700</v>
-      </c>
-      <c r="AB1">
+      <c r="AG1">
         <v>8800</v>
       </c>
-      <c r="AC1">
-        <v>8900</v>
-      </c>
-      <c r="AD1">
+      <c r="AH1">
         <v>9000</v>
       </c>
-      <c r="AE1">
-        <v>9100</v>
-      </c>
-      <c r="AF1">
+      <c r="AI1">
         <v>9200</v>
       </c>
-      <c r="AG1">
-        <v>9300</v>
-      </c>
-      <c r="AH1">
+      <c r="AJ1">
         <v>9400</v>
       </c>
-      <c r="AI1">
-        <v>9500</v>
-      </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>9600</v>
-      </c>
-      <c r="AK1">
-        <v>9700</v>
       </c>
       <c r="AL1">
         <v>9800</v>
@@ -543,597 +543,597 @@
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B2">
-        <v>40.229999999999997</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="C2">
-        <v>39.25</v>
+        <v>33.79</v>
       </c>
       <c r="D2">
-        <v>38.25</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="E2">
-        <v>37.229999999999997</v>
+        <v>32.630000000000003</v>
       </c>
       <c r="F2">
-        <v>36.200000000000003</v>
+        <v>32.07</v>
       </c>
       <c r="G2">
-        <v>35.15</v>
+        <v>31.52</v>
       </c>
       <c r="H2">
-        <v>34.08</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <v>33</v>
+        <v>30.51</v>
       </c>
       <c r="J2">
-        <v>31.92</v>
+        <v>30.06</v>
       </c>
       <c r="K2">
-        <v>30.86</v>
+        <v>29.66</v>
       </c>
       <c r="L2">
-        <v>29.86</v>
+        <v>29.32</v>
       </c>
       <c r="M2">
+        <v>29.05</v>
+      </c>
+      <c r="N2">
+        <v>28.86</v>
+      </c>
+      <c r="O2">
+        <v>28.73</v>
+      </c>
+      <c r="P2">
+        <v>28.68</v>
+      </c>
+      <c r="Q2">
+        <v>28.68</v>
+      </c>
+      <c r="R2">
+        <v>28.74</v>
+      </c>
+      <c r="S2">
+        <v>28.84</v>
+      </c>
+      <c r="T2">
         <v>28.97</v>
       </c>
-      <c r="N2">
-        <v>28.26</v>
-      </c>
-      <c r="O2">
-        <v>27.79</v>
-      </c>
-      <c r="P2">
-        <v>27.59</v>
-      </c>
-      <c r="Q2">
-        <v>27.61</v>
-      </c>
-      <c r="R2">
-        <v>27.81</v>
-      </c>
-      <c r="S2">
-        <v>28.14</v>
-      </c>
-      <c r="T2">
-        <v>28.54</v>
-      </c>
       <c r="U2">
-        <v>28.98</v>
+        <v>29.12</v>
       </c>
       <c r="V2">
-        <v>29.45</v>
+        <v>29.3</v>
       </c>
       <c r="W2">
-        <v>29.94</v>
+        <v>29.49</v>
       </c>
       <c r="X2">
-        <v>30.43</v>
+        <v>29.7</v>
       </c>
       <c r="Y2">
-        <v>30.91</v>
+        <v>29.91</v>
       </c>
       <c r="Z2">
-        <v>31.39</v>
+        <v>30.13</v>
       </c>
       <c r="AA2">
-        <v>31.87</v>
+        <v>30.35</v>
       </c>
       <c r="AB2">
-        <v>32.33</v>
+        <v>30.57</v>
       </c>
       <c r="AC2">
-        <v>32.79</v>
+        <v>30.8</v>
       </c>
       <c r="AD2">
+        <v>31.03</v>
+      </c>
+      <c r="AE2">
+        <v>31.26</v>
+      </c>
+      <c r="AF2">
+        <v>31.49</v>
+      </c>
+      <c r="AG2">
+        <v>31.94</v>
+      </c>
+      <c r="AH2">
+        <v>32.380000000000003</v>
+      </c>
+      <c r="AI2">
+        <v>32.82</v>
+      </c>
+      <c r="AJ2">
         <v>33.24</v>
       </c>
-      <c r="AE2">
-        <v>33.68</v>
-      </c>
-      <c r="AF2">
-        <v>34.119999999999997</v>
-      </c>
-      <c r="AG2">
-        <v>34.54</v>
-      </c>
-      <c r="AH2">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="AI2">
-        <v>35.36</v>
-      </c>
-      <c r="AJ2">
-        <v>35.76</v>
-      </c>
       <c r="AK2">
-        <v>36.14</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="AL2">
-        <v>36.520000000000003</v>
+        <v>34.06</v>
       </c>
       <c r="AM2">
-        <v>37.26</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B3">
-        <v>33.979999999999997</v>
+        <v>32.82</v>
       </c>
       <c r="C3">
-        <v>33.36</v>
+        <v>32.28</v>
       </c>
       <c r="D3">
-        <v>32.729999999999997</v>
+        <v>31.75</v>
       </c>
       <c r="E3">
-        <v>32.1</v>
+        <v>31.23</v>
       </c>
       <c r="F3">
-        <v>31.47</v>
+        <v>30.72</v>
       </c>
       <c r="G3">
-        <v>30.85</v>
+        <v>30.24</v>
       </c>
       <c r="H3">
-        <v>30.23</v>
+        <v>29.78</v>
       </c>
       <c r="I3">
-        <v>29.62</v>
+        <v>29.35</v>
       </c>
       <c r="J3">
-        <v>29.03</v>
+        <v>28.97</v>
       </c>
       <c r="K3">
-        <v>28.47</v>
+        <v>28.63</v>
       </c>
       <c r="L3">
-        <v>27.95</v>
+        <v>28.36</v>
       </c>
       <c r="M3">
-        <v>27.48</v>
+        <v>28.14</v>
       </c>
       <c r="N3">
-        <v>27.07</v>
+        <v>27.98</v>
       </c>
       <c r="O3">
-        <v>26.75</v>
+        <v>27.89</v>
       </c>
       <c r="P3">
-        <v>26.5</v>
+        <v>27.85</v>
       </c>
       <c r="Q3">
-        <v>26.34</v>
+        <v>27.86</v>
       </c>
       <c r="R3">
-        <v>26.26</v>
+        <v>27.92</v>
       </c>
       <c r="S3">
-        <v>26.25</v>
+        <v>28.01</v>
       </c>
       <c r="T3">
-        <v>26.3</v>
+        <v>28.13</v>
       </c>
       <c r="U3">
-        <v>26.39</v>
+        <v>28.27</v>
       </c>
       <c r="V3">
-        <v>26.52</v>
+        <v>28.44</v>
       </c>
       <c r="W3">
-        <v>26.68</v>
+        <v>28.61</v>
       </c>
       <c r="X3">
-        <v>26.86</v>
+        <v>28.8</v>
       </c>
       <c r="Y3">
-        <v>27.05</v>
+        <v>28.99</v>
       </c>
       <c r="Z3">
-        <v>27.26</v>
+        <v>29.19</v>
       </c>
       <c r="AA3">
-        <v>27.48</v>
+        <v>29.39</v>
       </c>
       <c r="AB3">
-        <v>27.7</v>
+        <v>29.6</v>
       </c>
       <c r="AC3">
-        <v>27.93</v>
+        <v>29.8</v>
       </c>
       <c r="AD3">
-        <v>28.15</v>
+        <v>30.01</v>
       </c>
       <c r="AE3">
-        <v>28.38</v>
+        <v>30.22</v>
       </c>
       <c r="AF3">
-        <v>28.61</v>
+        <v>30.43</v>
       </c>
       <c r="AG3">
-        <v>28.84</v>
+        <v>30.84</v>
       </c>
       <c r="AH3">
-        <v>29.07</v>
+        <v>31.25</v>
       </c>
       <c r="AI3">
-        <v>29.3</v>
+        <v>31.65</v>
       </c>
       <c r="AJ3">
-        <v>29.52</v>
+        <v>32.04</v>
       </c>
       <c r="AK3">
-        <v>29.74</v>
+        <v>32.43</v>
       </c>
       <c r="AL3">
-        <v>29.97</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AM3">
-        <v>30.4</v>
+        <v>33.159999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B4">
-        <v>31.78</v>
+        <v>30.01</v>
       </c>
       <c r="C4">
-        <v>31.26</v>
+        <v>29.65</v>
       </c>
       <c r="D4">
-        <v>30.75</v>
+        <v>29.3</v>
       </c>
       <c r="E4">
-        <v>30.24</v>
+        <v>28.96</v>
       </c>
       <c r="F4">
-        <v>29.75</v>
+        <v>28.64</v>
       </c>
       <c r="G4">
-        <v>29.26</v>
+        <v>28.33</v>
       </c>
       <c r="H4">
-        <v>28.79</v>
+        <v>28.04</v>
       </c>
       <c r="I4">
-        <v>28.35</v>
+        <v>27.78</v>
       </c>
       <c r="J4">
-        <v>27.93</v>
+        <v>27.54</v>
       </c>
       <c r="K4">
-        <v>27.55</v>
+        <v>27.32</v>
       </c>
       <c r="L4">
+        <v>27.13</v>
+      </c>
+      <c r="M4">
+        <v>26.97</v>
+      </c>
+      <c r="N4">
+        <v>26.83</v>
+      </c>
+      <c r="O4">
+        <v>26.73</v>
+      </c>
+      <c r="P4">
+        <v>26.65</v>
+      </c>
+      <c r="Q4">
+        <v>26.59</v>
+      </c>
+      <c r="R4">
+        <v>26.56</v>
+      </c>
+      <c r="S4">
+        <v>26.56</v>
+      </c>
+      <c r="T4">
+        <v>26.57</v>
+      </c>
+      <c r="U4">
+        <v>26.59</v>
+      </c>
+      <c r="V4">
+        <v>26.64</v>
+      </c>
+      <c r="W4">
+        <v>26.69</v>
+      </c>
+      <c r="X4">
+        <v>26.76</v>
+      </c>
+      <c r="Y4">
+        <v>26.84</v>
+      </c>
+      <c r="Z4">
+        <v>26.92</v>
+      </c>
+      <c r="AA4">
+        <v>27.01</v>
+      </c>
+      <c r="AB4">
+        <v>27.11</v>
+      </c>
+      <c r="AC4">
         <v>27.21</v>
       </c>
-      <c r="M4">
-        <v>26.92</v>
-      </c>
-      <c r="N4">
-        <v>26.68</v>
-      </c>
-      <c r="O4">
-        <v>26.5</v>
-      </c>
-      <c r="P4">
-        <v>26.38</v>
-      </c>
-      <c r="Q4">
-        <v>26.32</v>
-      </c>
-      <c r="R4">
-        <v>26.3</v>
-      </c>
-      <c r="S4">
-        <v>26.33</v>
-      </c>
-      <c r="T4">
-        <v>26.39</v>
-      </c>
-      <c r="U4">
-        <v>26.49</v>
-      </c>
-      <c r="V4">
-        <v>26.61</v>
-      </c>
-      <c r="W4">
-        <v>26.75</v>
-      </c>
-      <c r="X4">
-        <v>26.91</v>
-      </c>
-      <c r="Y4">
-        <v>27.07</v>
-      </c>
-      <c r="Z4">
-        <v>27.25</v>
-      </c>
-      <c r="AA4">
+      <c r="AD4">
+        <v>27.32</v>
+      </c>
+      <c r="AE4">
         <v>27.43</v>
       </c>
-      <c r="AB4">
-        <v>27.62</v>
-      </c>
-      <c r="AC4">
-        <v>27.81</v>
-      </c>
-      <c r="AD4">
-        <v>28.01</v>
-      </c>
-      <c r="AE4">
-        <v>28.2</v>
-      </c>
       <c r="AF4">
-        <v>28.4</v>
+        <v>27.54</v>
       </c>
       <c r="AG4">
-        <v>28.6</v>
+        <v>27.77</v>
       </c>
       <c r="AH4">
-        <v>28.79</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>28.99</v>
+        <v>28.24</v>
       </c>
       <c r="AJ4">
-        <v>29.18</v>
+        <v>28.48</v>
       </c>
       <c r="AK4">
-        <v>29.37</v>
+        <v>28.72</v>
       </c>
       <c r="AL4">
-        <v>29.57</v>
+        <v>28.95</v>
       </c>
       <c r="AM4">
-        <v>29.94</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="B5">
-        <v>28.57</v>
+        <v>27.87</v>
       </c>
       <c r="C5">
-        <v>28.2</v>
+        <v>27.57</v>
       </c>
       <c r="D5">
-        <v>27.84</v>
+        <v>27.29</v>
       </c>
       <c r="E5">
-        <v>27.5</v>
+        <v>27.02</v>
       </c>
       <c r="F5">
-        <v>27.18</v>
+        <v>26.78</v>
       </c>
       <c r="G5">
-        <v>26.87</v>
+        <v>26.56</v>
       </c>
       <c r="H5">
-        <v>26.59</v>
+        <v>26.36</v>
       </c>
       <c r="I5">
-        <v>26.34</v>
+        <v>26.18</v>
       </c>
       <c r="J5">
-        <v>26.11</v>
+        <v>26.02</v>
       </c>
       <c r="K5">
-        <v>25.92</v>
+        <v>25.89</v>
       </c>
       <c r="L5">
-        <v>25.75</v>
+        <v>25.79</v>
       </c>
       <c r="M5">
+        <v>25.7</v>
+      </c>
+      <c r="N5">
+        <v>25.64</v>
+      </c>
+      <c r="O5">
+        <v>25.6</v>
+      </c>
+      <c r="P5">
+        <v>25.58</v>
+      </c>
+      <c r="Q5">
+        <v>25.58</v>
+      </c>
+      <c r="R5">
+        <v>25.6</v>
+      </c>
+      <c r="S5">
         <v>25.63</v>
       </c>
-      <c r="N5">
-        <v>25.53</v>
-      </c>
-      <c r="O5">
-        <v>25.47</v>
-      </c>
-      <c r="P5">
-        <v>25.44</v>
-      </c>
-      <c r="Q5">
-        <v>25.43</v>
-      </c>
-      <c r="R5">
-        <v>25.45</v>
-      </c>
-      <c r="S5">
-        <v>25.5</v>
-      </c>
       <c r="T5">
-        <v>25.56</v>
+        <v>25.68</v>
       </c>
       <c r="U5">
-        <v>25.64</v>
+        <v>25.74</v>
       </c>
       <c r="V5">
-        <v>25.74</v>
+        <v>25.81</v>
       </c>
       <c r="W5">
-        <v>25.84</v>
+        <v>25.89</v>
       </c>
       <c r="X5">
-        <v>25.96</v>
+        <v>25.98</v>
       </c>
       <c r="Y5">
         <v>26.08</v>
       </c>
       <c r="Z5">
-        <v>26.21</v>
+        <v>26.19</v>
       </c>
       <c r="AA5">
-        <v>26.34</v>
+        <v>26.3</v>
       </c>
       <c r="AB5">
-        <v>26.48</v>
+        <v>26.41</v>
       </c>
       <c r="AC5">
-        <v>26.63</v>
+        <v>26.53</v>
       </c>
       <c r="AD5">
-        <v>26.77</v>
+        <v>26.66</v>
       </c>
       <c r="AE5">
-        <v>26.92</v>
+        <v>26.78</v>
       </c>
       <c r="AF5">
-        <v>27.06</v>
+        <v>26.91</v>
       </c>
       <c r="AG5">
-        <v>27.21</v>
+        <v>27.17</v>
       </c>
       <c r="AH5">
-        <v>27.36</v>
+        <v>27.44</v>
       </c>
       <c r="AI5">
-        <v>27.51</v>
+        <v>27.7</v>
       </c>
       <c r="AJ5">
-        <v>27.65</v>
+        <v>27.97</v>
       </c>
       <c r="AK5">
-        <v>27.8</v>
+        <v>28.24</v>
       </c>
       <c r="AL5">
-        <v>27.95</v>
+        <v>28.5</v>
       </c>
       <c r="AM5">
-        <v>28.24</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="B6">
-        <v>27.26</v>
+        <v>26.48</v>
       </c>
       <c r="C6">
-        <v>26.96</v>
+        <v>26.38</v>
       </c>
       <c r="D6">
-        <v>26.67</v>
+        <v>26.28</v>
       </c>
       <c r="E6">
-        <v>26.4</v>
+        <v>26.19</v>
       </c>
       <c r="F6">
-        <v>26.14</v>
+        <v>26.11</v>
       </c>
       <c r="G6">
-        <v>25.9</v>
+        <v>26.03</v>
       </c>
       <c r="H6">
-        <v>25.68</v>
+        <v>25.97</v>
       </c>
       <c r="I6">
-        <v>25.49</v>
+        <v>25.91</v>
       </c>
       <c r="J6">
-        <v>25.31</v>
+        <v>25.86</v>
       </c>
       <c r="K6">
-        <v>25.15</v>
+        <v>25.82</v>
       </c>
       <c r="L6">
-        <v>25.02</v>
+        <v>25.78</v>
       </c>
       <c r="M6">
-        <v>24.91</v>
+        <v>25.75</v>
       </c>
       <c r="N6">
-        <v>24.82</v>
+        <v>25.73</v>
       </c>
       <c r="O6">
-        <v>24.76</v>
+        <v>25.72</v>
       </c>
       <c r="P6">
-        <v>24.71</v>
+        <v>25.71</v>
       </c>
       <c r="Q6">
-        <v>24.69</v>
+        <v>25.71</v>
       </c>
       <c r="R6">
-        <v>24.68</v>
+        <v>25.71</v>
       </c>
       <c r="S6">
-        <v>24.69</v>
+        <v>25.72</v>
       </c>
       <c r="T6">
-        <v>24.71</v>
+        <v>25.73</v>
       </c>
       <c r="U6">
-        <v>24.74</v>
+        <v>25.75</v>
       </c>
       <c r="V6">
-        <v>24.79</v>
+        <v>25.77</v>
       </c>
       <c r="W6">
-        <v>24.85</v>
+        <v>25.79</v>
       </c>
       <c r="X6">
-        <v>24.91</v>
+        <v>25.82</v>
       </c>
       <c r="Y6">
-        <v>24.99</v>
+        <v>25.85</v>
       </c>
       <c r="Z6">
-        <v>25.07</v>
+        <v>25.89</v>
       </c>
       <c r="AA6">
-        <v>25.15</v>
+        <v>25.93</v>
       </c>
       <c r="AB6">
-        <v>25.24</v>
+        <v>25.97</v>
       </c>
       <c r="AC6">
-        <v>25.34</v>
+        <v>26.01</v>
       </c>
       <c r="AD6">
-        <v>25.44</v>
+        <v>26.05</v>
       </c>
       <c r="AE6">
-        <v>25.54</v>
+        <v>26.1</v>
       </c>
       <c r="AF6">
-        <v>25.64</v>
+        <v>26.15</v>
       </c>
       <c r="AG6">
-        <v>25.75</v>
+        <v>26.25</v>
       </c>
       <c r="AH6">
-        <v>25.85</v>
+        <v>26.36</v>
       </c>
       <c r="AI6">
-        <v>25.96</v>
+        <v>26.47</v>
       </c>
       <c r="AJ6">
-        <v>26.07</v>
+        <v>26.58</v>
       </c>
       <c r="AK6">
-        <v>26.18</v>
+        <v>26.7</v>
       </c>
       <c r="AL6">
-        <v>26.29</v>
+        <v>26.81</v>
       </c>
       <c r="AM6">
-        <v>26.51</v>
+        <v>26.93</v>
       </c>
     </row>
   </sheetData>
